--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127100419</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>127101642</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>127102449</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>127102299</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>127172557</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>127172562</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127172620</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127172558</v>
+        <v>127172612</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>127172606</v>
       </c>
       <c r="B10" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>127172617</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,45 +1780,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127172613</v>
+        <v>127172551</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Middagsflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529256</v>
+        <v>529186</v>
       </c>
       <c r="R12" t="n">
-        <v>7002044</v>
+        <v>7001822</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1867,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>4st blommande</t>
+          <t>2st födosökande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,57 +1894,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127172551</v>
+        <v>127172613</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Middagsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529186</v>
+        <v>529256</v>
       </c>
       <c r="R13" t="n">
-        <v>7001822</v>
+        <v>7002044</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2st födosökande</t>
+          <t>4st blommande</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,7 +1999,7 @@
         <v>127172619</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>127172608</v>
       </c>
       <c r="B15" t="n">
-        <v>92727</v>
+        <v>92802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127172561</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127172564</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127172607</v>
       </c>
       <c r="B18" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127172614</v>
       </c>
       <c r="B19" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172610</v>
+        <v>127172556</v>
       </c>
       <c r="B20" t="n">
-        <v>92727</v>
+        <v>92802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127100419</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>127101642</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>127102449</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>127102299</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172557</v>
+        <v>127172620</v>
       </c>
       <c r="B6" t="n">
-        <v>80114</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529167</v>
+        <v>529218</v>
       </c>
       <c r="R6" t="n">
-        <v>7002055</v>
+        <v>7001792</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,32 +1285,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172562</v>
+        <v>127172557</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529193</v>
+        <v>529167</v>
       </c>
       <c r="R7" t="n">
-        <v>7002084</v>
+        <v>7002055</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,11 +1356,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,32 +1382,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127172620</v>
+        <v>127172562</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529218</v>
+        <v>529193</v>
       </c>
       <c r="R8" t="n">
-        <v>7001792</v>
+        <v>7002084</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,6 +1453,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,32 +1484,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127172612</v>
+        <v>127172606</v>
       </c>
       <c r="B9" t="n">
-        <v>80114</v>
+        <v>80021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529167</v>
+        <v>529246</v>
       </c>
       <c r="R9" t="n">
-        <v>7002093</v>
+        <v>7002054</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,32 +1581,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172606</v>
+        <v>127172558</v>
       </c>
       <c r="B10" t="n">
-        <v>80018</v>
+        <v>80117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529246</v>
+        <v>529167</v>
       </c>
       <c r="R10" t="n">
-        <v>7002054</v>
+        <v>7002093</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1681,7 @@
         <v>127172617</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>127172613</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>127172619</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>127172608</v>
       </c>
       <c r="B15" t="n">
-        <v>92802</v>
+        <v>92808</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127172561</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127172564</v>
       </c>
       <c r="B17" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127172607</v>
       </c>
       <c r="B18" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127172614</v>
       </c>
       <c r="B19" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>127172556</v>
       </c>
       <c r="B20" t="n">
-        <v>92802</v>
+        <v>92808</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -1484,32 +1484,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127172606</v>
+        <v>127172612</v>
       </c>
       <c r="B9" t="n">
-        <v>80021</v>
+        <v>80117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529246</v>
+        <v>529167</v>
       </c>
       <c r="R9" t="n">
-        <v>7002054</v>
+        <v>7002093</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,32 +1581,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172558</v>
+        <v>127172606</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>80021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529167</v>
+        <v>529246</v>
       </c>
       <c r="R10" t="n">
-        <v>7002093</v>
+        <v>7002054</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -1484,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127172612</v>
+        <v>127172558</v>
       </c>
       <c r="B9" t="n">
         <v>80117</v>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>127101642</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>127102449</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>127102299</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,32 +1188,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172620</v>
+        <v>127172562</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529218</v>
+        <v>529193</v>
       </c>
       <c r="R6" t="n">
-        <v>7001792</v>
+        <v>7002084</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,6 +1259,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172557</v>
+        <v>127172620</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,21 +1301,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529167</v>
+        <v>529218</v>
       </c>
       <c r="R7" t="n">
-        <v>7002055</v>
+        <v>7001792</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,32 +1387,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127172562</v>
+        <v>127172557</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529193</v>
+        <v>529167</v>
       </c>
       <c r="R8" t="n">
-        <v>7002084</v>
+        <v>7002055</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,11 +1458,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,32 +1484,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127172558</v>
+        <v>127172606</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>80021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529167</v>
+        <v>529246</v>
       </c>
       <c r="R9" t="n">
-        <v>7002093</v>
+        <v>7002054</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,32 +1581,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172606</v>
+        <v>127172558</v>
       </c>
       <c r="B10" t="n">
-        <v>80021</v>
+        <v>80117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529246</v>
+        <v>529167</v>
       </c>
       <c r="R10" t="n">
-        <v>7002054</v>
+        <v>7002093</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1681,7 @@
         <v>127172617</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>127172613</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>127172608</v>
       </c>
       <c r="B15" t="n">
-        <v>92808</v>
+        <v>92809</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127172561</v>
       </c>
       <c r="B16" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127172564</v>
       </c>
       <c r="B17" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127172614</v>
       </c>
       <c r="B19" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>127172556</v>
       </c>
       <c r="B20" t="n">
-        <v>92808</v>
+        <v>92809</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -1188,32 +1188,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172562</v>
+        <v>127172557</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529193</v>
+        <v>529167</v>
       </c>
       <c r="R6" t="n">
-        <v>7002084</v>
+        <v>7002055</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,11 +1259,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1387,32 +1382,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127172557</v>
+        <v>127172562</v>
       </c>
       <c r="B8" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529167</v>
+        <v>529193</v>
       </c>
       <c r="R8" t="n">
-        <v>7002055</v>
+        <v>7002084</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,6 +1453,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,32 +1484,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127172606</v>
+        <v>127172558</v>
       </c>
       <c r="B9" t="n">
-        <v>80021</v>
+        <v>80117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529246</v>
+        <v>529167</v>
       </c>
       <c r="R9" t="n">
-        <v>7002054</v>
+        <v>7002093</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,32 +1581,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172558</v>
+        <v>127172606</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>80021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529167</v>
+        <v>529246</v>
       </c>
       <c r="R10" t="n">
-        <v>7002093</v>
+        <v>7002054</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2093,32 +2093,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127172608</v>
+        <v>127172561</v>
       </c>
       <c r="B15" t="n">
-        <v>92809</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529172</v>
+        <v>529185</v>
       </c>
       <c r="R15" t="n">
-        <v>7002049</v>
+        <v>7002105</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,6 +2164,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2190,32 +2195,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127172561</v>
+        <v>127172608</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>92809</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2225,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529185</v>
+        <v>529172</v>
       </c>
       <c r="R16" t="n">
-        <v>7002105</v>
+        <v>7002049</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,11 +2266,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -1188,32 +1188,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172557</v>
+        <v>127172562</v>
       </c>
       <c r="B6" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529167</v>
+        <v>529193</v>
       </c>
       <c r="R6" t="n">
-        <v>7002055</v>
+        <v>7002084</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,6 +1259,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1382,32 +1387,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127172562</v>
+        <v>127172557</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529193</v>
+        <v>529167</v>
       </c>
       <c r="R8" t="n">
-        <v>7002084</v>
+        <v>7002055</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,11 +1458,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127172558</v>
+        <v>127172612</v>
       </c>
       <c r="B9" t="n">
         <v>80117</v>
@@ -2093,32 +2093,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127172561</v>
+        <v>127172608</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>92809</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529185</v>
+        <v>529172</v>
       </c>
       <c r="R15" t="n">
-        <v>7002105</v>
+        <v>7002049</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,11 +2164,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,32 +2190,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127172608</v>
+        <v>127172561</v>
       </c>
       <c r="B16" t="n">
-        <v>92809</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2225,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529172</v>
+        <v>529185</v>
       </c>
       <c r="R16" t="n">
-        <v>7002049</v>
+        <v>7002105</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,6 +2261,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -1188,32 +1188,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172562</v>
+        <v>127172620</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529193</v>
+        <v>529218</v>
       </c>
       <c r="R6" t="n">
-        <v>7002084</v>
+        <v>7001792</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,11 +1259,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172620</v>
+        <v>127172557</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,21 +1296,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529218</v>
+        <v>529167</v>
       </c>
       <c r="R7" t="n">
-        <v>7001792</v>
+        <v>7002055</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1387,32 +1382,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127172557</v>
+        <v>127172562</v>
       </c>
       <c r="B8" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529167</v>
+        <v>529193</v>
       </c>
       <c r="R8" t="n">
-        <v>7002055</v>
+        <v>7002084</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,6 +1453,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -1780,57 +1780,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127172551</v>
+        <v>127172613</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Middagsflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529186</v>
+        <v>529256</v>
       </c>
       <c r="R12" t="n">
-        <v>7001822</v>
+        <v>7002044</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,7 +1855,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2st födosökande</t>
+          <t>4st blommande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,45 +1882,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127172613</v>
+        <v>127172551</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>57817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Middagsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529256</v>
+        <v>529186</v>
       </c>
       <c r="R13" t="n">
-        <v>7002044</v>
+        <v>7001822</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>4st blommande</t>
+          <t>2st födosökande</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127100419</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>127101642</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>127102449</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>127102299</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,32 +1188,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172620</v>
+        <v>127172562</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529218</v>
+        <v>529193</v>
       </c>
       <c r="R6" t="n">
-        <v>7001792</v>
+        <v>7002084</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,6 +1259,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172557</v>
+        <v>127172620</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,21 +1301,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529167</v>
+        <v>529218</v>
       </c>
       <c r="R7" t="n">
-        <v>7002055</v>
+        <v>7001792</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,32 +1387,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127172562</v>
+        <v>127172557</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>80121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529193</v>
+        <v>529167</v>
       </c>
       <c r="R8" t="n">
-        <v>7002084</v>
+        <v>7002055</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,11 +1458,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,7 +1487,7 @@
         <v>127172612</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>127172606</v>
       </c>
       <c r="B10" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>127172617</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,45 +1780,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127172613</v>
+        <v>127172551</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>57821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Middagsflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529256</v>
+        <v>529186</v>
       </c>
       <c r="R12" t="n">
-        <v>7002044</v>
+        <v>7001822</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1867,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>4st blommande</t>
+          <t>2st födosökande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,57 +1894,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127172551</v>
+        <v>127172613</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Middagsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529186</v>
+        <v>529256</v>
       </c>
       <c r="R13" t="n">
-        <v>7001822</v>
+        <v>7002044</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2st födosökande</t>
+          <t>4st blommande</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,7 +1999,7 @@
         <v>127172619</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>127172608</v>
       </c>
       <c r="B15" t="n">
-        <v>92809</v>
+        <v>92813</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127172561</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127172564</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127172607</v>
       </c>
       <c r="B18" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127172614</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>127172556</v>
       </c>
       <c r="B20" t="n">
-        <v>92809</v>
+        <v>92813</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -1188,32 +1188,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172562</v>
+        <v>127172620</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529193</v>
+        <v>529218</v>
       </c>
       <c r="R6" t="n">
-        <v>7002084</v>
+        <v>7001792</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,11 +1259,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172620</v>
+        <v>127172557</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,21 +1296,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529218</v>
+        <v>529167</v>
       </c>
       <c r="R7" t="n">
-        <v>7001792</v>
+        <v>7002055</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1387,32 +1382,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127172557</v>
+        <v>127172562</v>
       </c>
       <c r="B8" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529167</v>
+        <v>529193</v>
       </c>
       <c r="R8" t="n">
-        <v>7002055</v>
+        <v>7002084</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,6 +1453,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2093,32 +2093,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127172608</v>
+        <v>127172561</v>
       </c>
       <c r="B15" t="n">
-        <v>92813</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529172</v>
+        <v>529185</v>
       </c>
       <c r="R15" t="n">
-        <v>7002049</v>
+        <v>7002105</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,6 +2164,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2190,32 +2195,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127172561</v>
+        <v>127172608</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>92813</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2225,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529185</v>
+        <v>529172</v>
       </c>
       <c r="R16" t="n">
-        <v>7002105</v>
+        <v>7002049</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,11 +2266,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>127101642</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>127102449</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>127102299</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172620</v>
+        <v>127172557</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529218</v>
+        <v>529167</v>
       </c>
       <c r="R6" t="n">
-        <v>7001792</v>
+        <v>7002055</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172557</v>
+        <v>127172620</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,21 +1296,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529167</v>
+        <v>529218</v>
       </c>
       <c r="R7" t="n">
-        <v>7002055</v>
+        <v>7001792</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1385,7 +1385,7 @@
         <v>127172562</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>127172617</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>127172613</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2093,32 +2093,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127172561</v>
+        <v>127172608</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>92813</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529185</v>
+        <v>529172</v>
       </c>
       <c r="R15" t="n">
-        <v>7002105</v>
+        <v>7002049</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,11 +2164,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,32 +2190,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127172608</v>
+        <v>127172561</v>
       </c>
       <c r="B16" t="n">
-        <v>92813</v>
+        <v>98448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2225,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529172</v>
+        <v>529185</v>
       </c>
       <c r="R16" t="n">
-        <v>7002049</v>
+        <v>7002105</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,6 +2261,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2295,7 @@
         <v>127172564</v>
       </c>
       <c r="B17" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127172614</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127100419</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>127101642</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>127102449</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>127102299</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172557</v>
+        <v>127172620</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529167</v>
+        <v>529218</v>
       </c>
       <c r="R6" t="n">
-        <v>7002055</v>
+        <v>7001792</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172620</v>
+        <v>127172557</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,21 +1296,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529218</v>
+        <v>529167</v>
       </c>
       <c r="R7" t="n">
-        <v>7001792</v>
+        <v>7002055</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1385,7 +1385,7 @@
         <v>127172562</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127172612</v>
+        <v>127172558</v>
       </c>
       <c r="B9" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>127172606</v>
       </c>
       <c r="B10" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>127172617</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>127172551</v>
       </c>
       <c r="B12" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>127172613</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>127172619</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>127172608</v>
       </c>
       <c r="B15" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127172561</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127172564</v>
       </c>
       <c r="B17" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127172607</v>
       </c>
       <c r="B18" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127172614</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>127172556</v>
       </c>
       <c r="B20" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -1188,32 +1188,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172620</v>
+        <v>127172562</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529218</v>
+        <v>529193</v>
       </c>
       <c r="R6" t="n">
-        <v>7001792</v>
+        <v>7002084</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,6 +1259,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172557</v>
+        <v>127172620</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,21 +1301,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529167</v>
+        <v>529218</v>
       </c>
       <c r="R7" t="n">
-        <v>7002055</v>
+        <v>7001792</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,32 +1387,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127172562</v>
+        <v>127172557</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529193</v>
+        <v>529167</v>
       </c>
       <c r="R8" t="n">
-        <v>7002084</v>
+        <v>7002055</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,11 +1458,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127172558</v>
+        <v>127172612</v>
       </c>
       <c r="B9" t="n">
         <v>80123</v>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -1188,32 +1188,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172562</v>
+        <v>127172620</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529193</v>
+        <v>529218</v>
       </c>
       <c r="R6" t="n">
-        <v>7002084</v>
+        <v>7001792</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,11 +1259,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172620</v>
+        <v>127172557</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,21 +1296,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529218</v>
+        <v>529167</v>
       </c>
       <c r="R7" t="n">
-        <v>7001792</v>
+        <v>7002055</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1387,32 +1382,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127172557</v>
+        <v>127172562</v>
       </c>
       <c r="B8" t="n">
-        <v>80123</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529167</v>
+        <v>529193</v>
       </c>
       <c r="R8" t="n">
-        <v>7002055</v>
+        <v>7002084</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,6 +1453,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -1484,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127172612</v>
+        <v>127172558</v>
       </c>
       <c r="B9" t="n">
         <v>80123</v>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>127101642</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>127102449</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>127102299</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,32 +1188,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172620</v>
+        <v>127172562</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529218</v>
+        <v>529193</v>
       </c>
       <c r="R6" t="n">
-        <v>7001792</v>
+        <v>7002084</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,6 +1259,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172557</v>
+        <v>127172620</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,21 +1301,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529167</v>
+        <v>529218</v>
       </c>
       <c r="R7" t="n">
-        <v>7002055</v>
+        <v>7001792</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,32 +1387,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127172562</v>
+        <v>127172557</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529193</v>
+        <v>529167</v>
       </c>
       <c r="R8" t="n">
-        <v>7002084</v>
+        <v>7002055</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,11 +1458,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,32 +1484,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127172558</v>
+        <v>127172606</v>
       </c>
       <c r="B9" t="n">
-        <v>80123</v>
+        <v>80027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529167</v>
+        <v>529246</v>
       </c>
       <c r="R9" t="n">
-        <v>7002093</v>
+        <v>7002054</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,32 +1581,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172606</v>
+        <v>127172558</v>
       </c>
       <c r="B10" t="n">
-        <v>80027</v>
+        <v>80123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529246</v>
+        <v>529167</v>
       </c>
       <c r="R10" t="n">
-        <v>7002054</v>
+        <v>7002093</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1681,7 @@
         <v>127172617</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,57 +1780,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127172551</v>
+        <v>127172613</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Middagsflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529186</v>
+        <v>529256</v>
       </c>
       <c r="R12" t="n">
-        <v>7001822</v>
+        <v>7002044</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,7 +1855,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2st födosökande</t>
+          <t>4st blommande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,45 +1882,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127172613</v>
+        <v>127172551</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Middagsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529256</v>
+        <v>529186</v>
       </c>
       <c r="R13" t="n">
-        <v>7002044</v>
+        <v>7001822</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>4st blommande</t>
+          <t>2st födosökande</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,7 +2096,7 @@
         <v>127172608</v>
       </c>
       <c r="B15" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127172561</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127172564</v>
       </c>
       <c r="B17" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127172614</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>127172556</v>
       </c>
       <c r="B20" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127100419</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>127101642</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>127102449</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>127102299</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,32 +1188,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172562</v>
+        <v>127172620</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529193</v>
+        <v>529218</v>
       </c>
       <c r="R6" t="n">
-        <v>7002084</v>
+        <v>7001792</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,11 +1259,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172620</v>
+        <v>127172557</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>80126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,21 +1296,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529218</v>
+        <v>529167</v>
       </c>
       <c r="R7" t="n">
-        <v>7001792</v>
+        <v>7002055</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1387,32 +1382,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127172557</v>
+        <v>127172562</v>
       </c>
       <c r="B8" t="n">
-        <v>80123</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529167</v>
+        <v>529193</v>
       </c>
       <c r="R8" t="n">
-        <v>7002055</v>
+        <v>7002084</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,6 +1453,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,32 +1484,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127172606</v>
+        <v>127172612</v>
       </c>
       <c r="B9" t="n">
-        <v>80027</v>
+        <v>80126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529246</v>
+        <v>529167</v>
       </c>
       <c r="R9" t="n">
-        <v>7002054</v>
+        <v>7002093</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,32 +1581,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172558</v>
+        <v>127172606</v>
       </c>
       <c r="B10" t="n">
-        <v>80123</v>
+        <v>80030</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529167</v>
+        <v>529246</v>
       </c>
       <c r="R10" t="n">
-        <v>7002093</v>
+        <v>7002054</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1681,7 @@
         <v>127172617</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,45 +1780,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127172613</v>
+        <v>127172551</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Middagsflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529256</v>
+        <v>529186</v>
       </c>
       <c r="R12" t="n">
-        <v>7002044</v>
+        <v>7001822</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1867,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>4st blommande</t>
+          <t>2st födosökande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,57 +1894,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127172551</v>
+        <v>127172613</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Middagsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529186</v>
+        <v>529256</v>
       </c>
       <c r="R13" t="n">
-        <v>7001822</v>
+        <v>7002044</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2st födosökande</t>
+          <t>4st blommande</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,7 +1999,7 @@
         <v>127172619</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>127172608</v>
       </c>
       <c r="B15" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127172561</v>
       </c>
       <c r="B16" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127172564</v>
       </c>
       <c r="B17" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127172607</v>
       </c>
       <c r="B18" t="n">
-        <v>80027</v>
+        <v>80030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127172614</v>
       </c>
       <c r="B19" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>127172556</v>
       </c>
       <c r="B20" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127100419</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>127101642</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>127102449</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>127102299</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>127172620</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>127172557</v>
       </c>
       <c r="B7" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127172562</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,32 +1484,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127172612</v>
+        <v>127172606</v>
       </c>
       <c r="B9" t="n">
-        <v>80126</v>
+        <v>80036</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529167</v>
+        <v>529246</v>
       </c>
       <c r="R9" t="n">
-        <v>7002093</v>
+        <v>7002054</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,32 +1581,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172606</v>
+        <v>127172558</v>
       </c>
       <c r="B10" t="n">
-        <v>80030</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529246</v>
+        <v>529167</v>
       </c>
       <c r="R10" t="n">
-        <v>7002054</v>
+        <v>7002093</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1681,7 @@
         <v>127172617</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>127172551</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>127172613</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>127172619</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>127172608</v>
       </c>
       <c r="B15" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127172561</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127172564</v>
       </c>
       <c r="B17" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127172607</v>
       </c>
       <c r="B18" t="n">
-        <v>80030</v>
+        <v>80036</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127172614</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>127172556</v>
       </c>
       <c r="B20" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -1385,7 +1385,7 @@
         <v>127172562</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,32 +1484,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127172606</v>
+        <v>127172612</v>
       </c>
       <c r="B9" t="n">
-        <v>80036</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529246</v>
+        <v>529167</v>
       </c>
       <c r="R9" t="n">
-        <v>7002054</v>
+        <v>7002093</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,32 +1581,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127172558</v>
+        <v>127172606</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>80036</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529167</v>
+        <v>529246</v>
       </c>
       <c r="R10" t="n">
-        <v>7002093</v>
+        <v>7002054</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1681,7 @@
         <v>127172617</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>127172613</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>127172608</v>
       </c>
       <c r="B15" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127172561</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127172564</v>
       </c>
       <c r="B17" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127172614</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>127172556</v>
       </c>
       <c r="B20" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127100419</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>127101642</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>127102449</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>127102299</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172620</v>
+        <v>127172557</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>80114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529218</v>
+        <v>529167</v>
       </c>
       <c r="R6" t="n">
-        <v>7001792</v>
+        <v>7002055</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,32 +1285,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172557</v>
+        <v>127172562</v>
       </c>
       <c r="B7" t="n">
-        <v>80132</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529167</v>
+        <v>529193</v>
       </c>
       <c r="R7" t="n">
-        <v>7002055</v>
+        <v>7002084</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,6 +1356,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,32 +1387,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127172562</v>
+        <v>127172620</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529193</v>
+        <v>529218</v>
       </c>
       <c r="R8" t="n">
-        <v>7002084</v>
+        <v>7001792</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,11 +1458,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,7 +1487,7 @@
         <v>127172612</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>127172606</v>
       </c>
       <c r="B10" t="n">
-        <v>80036</v>
+        <v>80018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>127172617</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>127172551</v>
       </c>
       <c r="B12" t="n">
-        <v>57832</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>127172613</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>127172619</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>127172608</v>
       </c>
       <c r="B15" t="n">
-        <v>92833</v>
+        <v>92802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127172561</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127172564</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127172607</v>
       </c>
       <c r="B18" t="n">
-        <v>80036</v>
+        <v>80018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127172614</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>127172556</v>
       </c>
       <c r="B20" t="n">
-        <v>92833</v>
+        <v>92802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34317-2025 artfynd.xlsx
+++ b/artfynd/A 34317-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127100419</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>127101642</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>127102449</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>127102299</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172557</v>
+        <v>127172620</v>
       </c>
       <c r="B6" t="n">
-        <v>80114</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529167</v>
+        <v>529218</v>
       </c>
       <c r="R6" t="n">
-        <v>7002055</v>
+        <v>7001792</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,32 +1285,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172562</v>
+        <v>127172557</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529193</v>
+        <v>529167</v>
       </c>
       <c r="R7" t="n">
-        <v>7002084</v>
+        <v>7002055</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,11 +1356,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,32 +1382,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127172620</v>
+        <v>127172562</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529218</v>
+        <v>529193</v>
       </c>
       <c r="R8" t="n">
-        <v>7001792</v>
+        <v>7002084</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,6 +1453,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,7 +1487,7 @@
         <v>127172612</v>
       </c>
       <c r="B9" t="n">
-        <v>80114</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>127172606</v>
       </c>
       <c r="B10" t="n">
-        <v>80018</v>
+        <v>80036</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>127172617</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>127172551</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>57832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>127172613</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>127172619</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>127172608</v>
       </c>
       <c r="B15" t="n">
-        <v>92802</v>
+        <v>92833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127172561</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>127172564</v>
       </c>
       <c r="B17" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127172607</v>
       </c>
       <c r="B18" t="n">
-        <v>80018</v>
+        <v>80036</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127172614</v>
       </c>
       <c r="B19" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>127172556</v>
       </c>
       <c r="B20" t="n">
-        <v>92802</v>
+        <v>92833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
